--- a/marketing_forms/004_market_sizing_template--marketing_forms.xlsx
+++ b/marketing_forms/004_market_sizing_template--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>market entry barrier</t>
+          <t>Market Entry Barriers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>competitive_position</t>
+          <t>competitive_position_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>competitive position</t>
+          <t>Competitive Position 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>market_segment</t>
+          <t>market_segment_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>market segment</t>
+          <t>Market Segment 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>time_in_market</t>
+          <t>time_in_market_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>time in market</t>
+          <t>Time In Market 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>revenue_streams</t>
+          <t>revenue_streams_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>revenue streams</t>
+          <t>Revenue Streams 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>market_entry_barrier</t>
+          <t>market_entry_barrier_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>market entry barrier</t>
+          <t>Market Entry Barrier 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>competitive_position</t>
+          <t>competitive_position_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>competitive position</t>
+          <t>Competitive Position 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>market_growth_rate</t>
+          <t>market_growth_rate_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>market growth rate</t>
+          <t>Market Growth Rate 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>revenue_streams</t>
+          <t>revenue_streams_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>revenue streams</t>
+          <t>Revenue Streams 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
   <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1608,7 +1608,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>competitive_position_choices</t>
+          <t>competitive_position_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>competitive_position_choices</t>
+          <t>competitive_position_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>competitive_position_choices</t>
+          <t>competitive_position_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>market_segment_choices</t>
+          <t>market_segment_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>market_segment_choices</t>
+          <t>market_segment_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>market_segment_choices</t>
+          <t>market_segment_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>market_segment_choices</t>
+          <t>market_segment_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>revenue_streams_choices</t>
+          <t>revenue_streams_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>revenue_streams_choices</t>
+          <t>revenue_streams_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>revenue_streams_choices</t>
+          <t>revenue_streams_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>market_entry_barrier_choices</t>
+          <t>market_entry_barrier_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>market_entry_barrier_choices</t>
+          <t>market_entry_barrier_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>market_entry_barrier_choices</t>
+          <t>market_entry_barrier_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1829,7 +1829,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>competitive_position_choices</t>
+          <t>competitive_position_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>competitive_position_choices</t>
+          <t>competitive_position_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>competitive_position_choices</t>
+          <t>competitive_position_3_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1880,7 +1880,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>revenue_streams_choices</t>
+          <t>revenue_streams_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>revenue_streams_choices</t>
+          <t>revenue_streams_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1914,7 +1914,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>revenue_streams_choices</t>
+          <t>revenue_streams_3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
